--- a/34th_Backgammon-championships_4a_output.xlsx
+++ b/34th_Backgammon-championships_4a_output.xlsx
@@ -1141,7 +1141,7 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -1150,13 +1150,13 @@
         <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P4" t="n">
         <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
         <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>6</v>
@@ -1202,7 +1202,7 @@
         <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M5" t="n">
         <v>4</v>
@@ -1211,7 +1211,7 @@
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
         <v>6</v>
@@ -1269,7 +1269,7 @@
         <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
@@ -1303,7 +1303,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
         <v>11</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>9</v>
@@ -1455,7 +1455,7 @@
         <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P9" t="n">
         <v>9</v>
@@ -1486,7 +1486,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
@@ -1528,7 +1528,7 @@
         <v>9</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
         <v>4</v>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
@@ -1583,7 +1583,7 @@
         <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
         <v>11</v>
@@ -1641,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -1678,7 +1678,7 @@
         <v>7</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>4</v>
@@ -1690,7 +1690,7 @@
         <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K13" t="n">
         <v>9</v>
